--- a/assets/data/excel/skills.xlsx
+++ b/assets/data/excel/skills.xlsx
@@ -1013,14 +1013,19 @@
         <v>0.9</v>
       </c>
       <c r="J9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K9" t="n">
         <v>4</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>["lifesteal:0.30", "lostBonus:0.20"]</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>["lifesteal:0.30","bonusDamageVsLost:0.20"]</t>
         </is>
       </c>
     </row>

--- a/assets/data/excel/skills.xlsx
+++ b/assets/data/excel/skills.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,6 +528,16 @@
           <t>additionalEffects</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>maxLevel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>levelUpBonus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -595,6 +605,16 @@
           <t>array</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -662,6 +682,16 @@
           <t>附加效果列表</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>技能最大等级</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>技能升级效果配置</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -723,6 +753,14 @@
           <t>["damageReduction:0.10"]</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.05}, {"level": 5, "multiplierBonus": 0.05}, {"level": 6, "multiplierBonus": 0.1}]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -784,6 +822,14 @@
           <t>["atkDebuff:0.08:allEnemy"]</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.1}, {"level": 3, "multiplierBonus": 0.1, "unlockEffect": {"type": "bleed", "value": 0.05, "duration": 2}}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1, "effectBoost": {"type": "bleed", "valueBonus": 0.05}}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -845,6 +891,14 @@
           <t>["stun:1", "splashDamage:0.50"]</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.15}, {"level": 3, "multiplierBonus": 0.15, "cooldownReduce": 1}, {"level": 4, "multiplierBonus": 0.15}, {"level": 5, "multiplierBonus": 0.15, "cooldownReduce": 1}, {"level": 6, "multiplierBonus": 0.25, "targetBoost": "allEnemies"}]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -906,6 +960,14 @@
           <t>["defBoost:0.40", "taunt:allEnemy", "counter:0.15:0.60"]</t>
         </is>
       </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -967,6 +1029,14 @@
           <t>["spdDebuff:0.20:allEnemy", "groundBonus:0.15"]</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>6</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1028,6 +1098,14 @@
           <t>["lifesteal:0.30","bonusDamageVsLost:0.20"]</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1089,6 +1167,14 @@
           <t>["hpBoost:0.20", "lowHpDR:0.15:0.30"]</t>
         </is>
       </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1150,6 +1236,14 @@
           <t>["counterChance:0.20"]</t>
         </is>
       </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1211,6 +1305,14 @@
           <t>["teamHeal:0.05", "teamDefBoost:0.05"]</t>
         </is>
       </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1272,6 +1374,14 @@
           <t>["armorPen:0.25"]</t>
         </is>
       </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.05}, {"level": 5, "multiplierBonus": 0.05}, {"level": 6, "multiplierBonus": 0.1}]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1333,6 +1443,14 @@
           <t>["poison:3:0.15"]</t>
         </is>
       </c>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.1}, {"level": 3, "multiplierBonus": 0.1, "unlockEffect": {"type": "weakness", "value": 0.1, "duration": 2}}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1, "effectBoost": {"type": "weakness", "valueBonus": 0.05}}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1394,6 +1512,14 @@
           <t>["critBoost:0.50", "critDmgBoost:0.30"]</t>
         </is>
       </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.15}, {"level": 3, "multiplierBonus": 0.15, "cooldownReduce": 1}, {"level": 4, "multiplierBonus": 0.15}, {"level": 5, "multiplierBonus": 0.15, "cooldownReduce": 1}, {"level": 6, "multiplierBonus": 0.25, "targetBoost": "allEnemies"}]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1455,6 +1581,14 @@
           <t>["burnChance:0.30:2:0.10"]</t>
         </is>
       </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1516,6 +1650,14 @@
           <t>["executeBonus:0.40:0.40", "executeCrit"]</t>
         </is>
       </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1577,6 +1719,14 @@
           <t>["chainCount:4", "chainDecay:0.10"]</t>
         </is>
       </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1638,6 +1788,14 @@
           <t>["critBoost:0.15", "critDmgBoost:0.25", "lowHpCritBoost:0.10:0.50"]</t>
         </is>
       </c>
+      <c r="N19" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1699,6 +1857,14 @@
           <t>["killAtkBoost:0.08:5", "killSpdBoost:0.05:5", "maxStackExtraTurn"]</t>
         </is>
       </c>
+      <c r="N20" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1760,6 +1926,14 @@
           <t>["trueDmgChance:0.10:0.05:2.0"]</t>
         </is>
       </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1821,6 +1995,14 @@
           <t>["healPercent:0.25", "hot:2:0.08", "cleanse:1"]</t>
         </is>
       </c>
+      <c r="N22" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.05}, {"level": 5, "multiplierBonus": 0.05}, {"level": 6, "multiplierBonus": 0.1}]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1882,6 +2064,14 @@
           <t>["atkBoost:0.25", "critBoost:0.15", "damageReduction:0.10"]</t>
         </is>
       </c>
+      <c r="N23" t="n">
+        <v>6</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.1}, {"level": 3, "multiplierBonus": 0.1, "unlockEffect": {"type": "blind", "value": 0.1, "duration": 1}}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1, "effectBoost": {"type": "blind", "valueBonus": 0.05}}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1943,6 +2133,14 @@
           <t>["teamHeal:0.12", "teamHot:3:0.05", "teamSpdBoost:0.10"]</t>
         </is>
       </c>
+      <c r="N24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.15}, {"level": 3, "multiplierBonus": 0.15, "cooldownReduce": 1}, {"level": 4, "multiplierBonus": 0.15}, {"level": 5, "multiplierBonus": 0.15, "cooldownReduce": 1}, {"level": 6, "multiplierBonus": 0.25, "targetBoost": "allEnemies"}]</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2004,6 +2202,14 @@
           <t>["atkDebuff:0.15:allEnemy", "spdDebuff:0.12:allEnemy", "failChance:0.20"]</t>
         </is>
       </c>
+      <c r="N25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2065,6 +2271,14 @@
           <t>["emergencyHeal:0.40:0.30", "undying:2"]</t>
         </is>
       </c>
+      <c r="N26" t="n">
+        <v>6</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2126,6 +2340,14 @@
           <t>["damageToHeal:0.50"]</t>
         </is>
       </c>
+      <c r="N27" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2187,6 +2409,14 @@
           <t>["healBoost:0.20", "healToAtk:0.15"]</t>
         </is>
       </c>
+      <c r="N28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2248,6 +2478,14 @@
           <t>["teamDodgeBoost:0.08", "lethalShield:0.25:0.20:1"]</t>
         </is>
       </c>
+      <c r="N29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2309,6 +2547,14 @@
           <t>["autoCleanse:1", "debuffReduce:1"]</t>
         </is>
       </c>
+      <c r="N30" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>[{"level": 2, "multiplierBonus": 0.05}, {"level": 3, "multiplierBonus": 0.05}, {"level": 4, "multiplierBonus": 0.1}, {"level": 5, "multiplierBonus": 0.1}, {"level": 6, "multiplierBonus": 0.15}]</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2370,6 +2616,14 @@
           <t>["splashDamage:0.80"]</t>
         </is>
       </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2431,6 +2685,14 @@
           <t>["atkBoost:0.30", "maxHpDmg:0.05"]</t>
         </is>
       </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2492,6 +2754,14 @@
           <t>["spdDebuff:0.25:allEnemy"]</t>
         </is>
       </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2553,6 +2823,14 @@
           <t>["atkDebuff:0.20:allEnemy"]</t>
         </is>
       </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2614,6 +2892,14 @@
           <t>["multiHit:3:0.80"]</t>
         </is>
       </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2675,6 +2961,14 @@
           <t>["bind:allEnemy:1"]</t>
         </is>
       </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2736,6 +3030,14 @@
           <t>["hpDrain:0.10"]</t>
         </is>
       </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2797,6 +3099,14 @@
           <t>["poison:3:0.04:maxHp"]</t>
         </is>
       </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2858,6 +3168,14 @@
           <t>["teamLifesteal:0.40"]</t>
         </is>
       </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2919,6 +3237,14 @@
           <t>["armorPen:0.30"]</t>
         </is>
       </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2980,6 +3306,14 @@
           <t>["shieldPercent:0.25", "shieldBreakDmg:1.0"]</t>
         </is>
       </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3041,6 +3375,14 @@
           <t>["defDebuff:0.20:allEnemy"]</t>
         </is>
       </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3102,6 +3444,14 @@
           <t>["armorPen:0.40", "sureHit"]</t>
         </is>
       </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3163,6 +3513,14 @@
           <t>["teamAtkBoost:0.25", "teamCritBoost:0.20"]</t>
         </is>
       </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3224,6 +3582,14 @@
           <t>["burnChance:0.25:2"]</t>
         </is>
       </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3285,6 +3651,14 @@
           <t>["illusionBonus:0.50"]</t>
         </is>
       </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3346,6 +3720,14 @@
           <t>["hitDebuff:0.30:allEnemy"]</t>
         </is>
       </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3407,6 +3789,14 @@
           <t>["healPercent:0.20", "cleanseAll", "damageReduction:0.10"]</t>
         </is>
       </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3468,6 +3858,14 @@
           <t>["multiHit:4:0.375", "stunChance:0.15:1"]</t>
         </is>
       </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3529,6 +3927,14 @@
           <t>["stunBonus:0.60"]</t>
         </is>
       </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3590,6 +3996,14 @@
           <t>["selfStun:1", "selfDefBoost:0.50"]</t>
         </is>
       </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3651,6 +4065,14 @@
           <t>["teamCleanseAll"]</t>
         </is>
       </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3712,6 +4134,14 @@
           <t>["teamShield:0.20", "ccImmune:3"]</t>
         </is>
       </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3773,6 +4203,14 @@
           <t>["buffBonus:0.15"]</t>
         </is>
       </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3834,6 +4272,14 @@
           <t>["radiationDot:3:0.03:maxHp"]</t>
         </is>
       </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3895,6 +4341,14 @@
           <t>["stealBuff:1:0.10"]</t>
         </is>
       </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3956,6 +4410,14 @@
           <t>["randomTeleport:2", "spdDebuff:0.30:2"]</t>
         </is>
       </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4017,6 +4479,14 @@
           <t>["pierceSplash:1.5"]</t>
         </is>
       </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4078,6 +4548,14 @@
           <t>["defDebuff:0.30:allEnemy:3"]</t>
         </is>
       </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4139,6 +4617,14 @@
           <t>["healPercent:0.15", "cooldownReset", "omegaStack:0.10:3"]</t>
         </is>
       </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4200,6 +4686,14 @@
           <t>["burn:2:0.05"]</t>
         </is>
       </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4261,6 +4755,14 @@
           <t>["sureHit", "targetLowestHp"]</t>
         </is>
       </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4322,6 +4824,14 @@
           <t>["armorPen:0.20"]</t>
         </is>
       </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4383,6 +4893,14 @@
           <t>["defBoost:0.50", "taunt:allEnemy"]</t>
         </is>
       </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4444,6 +4962,14 @@
           <t>["hitDebuff:0.20:allEnemy"]</t>
         </is>
       </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4505,6 +5031,14 @@
           <t>["defDebuff:0.25:3"]</t>
         </is>
       </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4566,6 +5100,14 @@
           <t>["defDebuffChance:0.30:0.15:2"]</t>
         </is>
       </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4627,6 +5169,14 @@
           <t>["vulnUp:0.15:allEnemy:2"]</t>
         </is>
       </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4688,6 +5238,14 @@
           <t>["ccBonus:0.40"]</t>
         </is>
       </c>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4749,6 +5307,14 @@
           <t>["spdDebuff:0.20:allEnemy"]</t>
         </is>
       </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4810,6 +5376,14 @@
           <t>["erosion:3:0.08"]</t>
         </is>
       </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4871,6 +5445,14 @@
           <t>["healPercent:0.20", "aoeOnHeal:0.80"]</t>
         </is>
       </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4932,6 +5514,14 @@
           <t>["stunChance:0.20:1"]</t>
         </is>
       </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4993,6 +5583,14 @@
           <t>["atkBoost:0.30", "spdBoost:0.20", "bonusAttack:1.0"]</t>
         </is>
       </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5054,6 +5652,14 @@
           <t>["critDebuff:0.25:allEnemy"]</t>
         </is>
       </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5115,6 +5721,14 @@
           <t>["dodgeReset:1"]</t>
         </is>
       </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5176,6 +5790,14 @@
           <t>["radiationDot:3:0.02:maxHp"]</t>
         </is>
       </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5237,6 +5859,14 @@
           <t>["shieldPercent:0.30", "defBoost:0.30"]</t>
         </is>
       </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5298,6 +5928,14 @@
           <t>["spdDebuff:0.40:2"]</t>
         </is>
       </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5357,6 +5995,14 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>["selfDebuff:def:0.30:1"]</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>

--- a/assets/data/excel/skills.xlsx
+++ b/assets/data/excel/skills.xlsx
@@ -1079,8 +1079,10 @@
           <t>dark</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0.9</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
       </c>
       <c r="J9" t="n">
         <v>0.9</v>
